--- a/Config/Excel/role.xlsx
+++ b/Config/Excel/role.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="17">
   <si>
     <t>id</t>
   </si>
@@ -46,6 +46,9 @@
     <t>headIcon</t>
   </si>
   <si>
+    <t>container</t>
+  </si>
+  <si>
     <t>c</t>
   </si>
   <si>
@@ -61,13 +64,22 @@
     <t>xxxx</t>
   </si>
   <si>
-    <t>主角</t>
-  </si>
-  <si>
-    <t>System/Role/Role001</t>
+    <t>一号</t>
+  </si>
+  <si>
+    <t>Assets/Bundles/Role/PlayerActor/actor1001</t>
   </si>
   <si>
     <t>fsfsfs</t>
+  </si>
+  <si>
+    <t>land</t>
+  </si>
+  <si>
+    <t>二号</t>
+  </si>
+  <si>
+    <t>Assets/Bundles/Role/PlayerActor/actor1002</t>
   </si>
 </sst>
 </file>
@@ -1041,13 +1053,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="24.5" customWidth="1"/>
+    <col min="3" max="3" width="42.375" customWidth="1"/>
+    <col min="6" max="6" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1063,73 +1076,105 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5">
-        <v>2001</v>
+        <v>1001</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>1002</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/role.xlsx
+++ b/Config/Excel/role.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
   <si>
     <t>id</t>
   </si>
@@ -80,6 +80,15 @@
   </si>
   <si>
     <t>Assets/Bundles/Role/PlayerActor/actor1002</t>
+  </si>
+  <si>
+    <t>三号</t>
+  </si>
+  <si>
+    <t>四号</t>
+  </si>
+  <si>
+    <t>五号</t>
   </si>
 </sst>
 </file>
@@ -1053,8 +1062,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="5"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="42.375" customWidth="1"/>
     <col min="6" max="6" width="10.625" customWidth="1"/>
@@ -1174,6 +1183,57 @@
         <v>13</v>
       </c>
       <c r="F6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>1003</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>1004</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>1005</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Config/Excel/role.xlsx
+++ b/Config/Excel/role.xlsx
@@ -67,7 +67,7 @@
     <t>一号</t>
   </si>
   <si>
-    <t>Assets/Bundles/Role/PlayerActor/actor1001</t>
+    <t>Assets/Bundles/Character/Actor/PlayerActor/actor1001</t>
   </si>
   <si>
     <t>fsfsfs</t>
@@ -79,7 +79,7 @@
     <t>二号</t>
   </si>
   <si>
-    <t>Assets/Bundles/Role/PlayerActor/actor1002</t>
+    <t>Assets/Bundles/Character/Actor/PlayerActor/actor1002</t>
   </si>
   <si>
     <t>三号</t>

--- a/Config/Excel/role.xlsx
+++ b/Config/Excel/role.xlsx
@@ -1065,7 +1065,7 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="42.375" customWidth="1"/>
+    <col min="3" max="3" width="57.75" customWidth="1"/>
     <col min="6" max="6" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>

--- a/Config/Excel/role.xlsx
+++ b/Config/Excel/role.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="19">
   <si>
     <t>id</t>
   </si>
@@ -37,7 +37,7 @@
     <t>name</t>
   </si>
   <si>
-    <t>prefabPath</t>
+    <t>actor</t>
   </si>
   <si>
     <t>roleType</t>
@@ -61,15 +61,15 @@
     <t>xxx</t>
   </si>
   <si>
+    <t>预制件</t>
+  </si>
+  <si>
     <t>xxxx</t>
   </si>
   <si>
     <t>一号</t>
   </si>
   <si>
-    <t>Assets/Bundles/Character/Actor/PlayerActor/actor1001</t>
-  </si>
-  <si>
     <t>fsfsfs</t>
   </si>
   <si>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t>二号</t>
-  </si>
-  <si>
-    <t>Assets/Bundles/Character/Actor/PlayerActor/actor1002</t>
   </si>
   <si>
     <t>三号</t>
@@ -711,8 +708,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1065,7 +1062,6 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="57.75" customWidth="1"/>
     <col min="6" max="6" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1076,7 +1072,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -1096,7 +1092,7 @@
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D2" t="s">
@@ -1116,8 +1112,8 @@
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -1136,14 +1132,14 @@
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1151,10 +1147,10 @@
         <v>1001</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
         <v>12</v>
+      </c>
+      <c r="C5" s="2">
+        <v>300001</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1173,8 +1169,8 @@
       <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
-        <v>16</v>
+      <c r="C6" s="2">
+        <v>300002</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1191,10 +1187,10 @@
         <v>1003</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="C7" s="2">
+        <v>300003</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1208,10 +1204,10 @@
         <v>1004</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="C8" s="2">
+        <v>300004</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1225,10 +1221,10 @@
         <v>1005</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="C9" s="2">
+        <v>300005</v>
       </c>
       <c r="D9">
         <v>1</v>
